--- a/public/templates/examples/A-015-IncidentClassificationSeverityMatrix-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-015-IncidentClassificationSeverityMatrix-EXAMPLE-L.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="20160" windowHeight="20280" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -205,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -272,6 +274,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -726,7 +731,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9" ht="50.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Defines the severity tiers used to classify a cybersecurity incident, the kinds of incident that fall in each tier, and the notification timing and response each tier triggers. It is the companion to the Incident Response Plan and the basis the Incident Notification &amp; Escalation Contact List works from. Scope: all incidents affecting Agency public-safety systems, including CAD, call handling, GIS, and systems reached through IDACS.</t>
@@ -744,7 +749,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="8" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Each row is one severity tier, from Sev 1 (most severe) to Sev 4 (least). For each tier the columns give its definition and impact, example incidents, the notification timing it triggers, and the escalation and response protocol. Classify an incident at the highest tier that any single column matches.</t>
@@ -789,7 +794,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="74" customHeight="1">
+    <row r="18" ht="129.7" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
           <t>Sev 1: Critical</t>
@@ -897,15 +902,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+    <row r="22">
+      <c r="A22"/>
       <c r="B22" s="12" t="n"/>
       <c r="C22" s="12" t="n"/>
       <c r="D22" s="12" t="n"/>
       <c r="E22" s="12" t="n"/>
     </row>
-    <row r="23" ht="19.5" customHeight="1">
-      <c r="A23" s="11" t="n"/>
+    <row r="23">
+      <c r="A23"/>
       <c r="B23" s="12" t="n"/>
       <c r="C23" s="12" t="n"/>
       <c r="D23" s="12" t="n"/>
@@ -922,7 +927,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="8" t="n"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="34.7" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Any suspected compromise of CJIS data is escalated to Sev 1 regardless of other factors. The Information Security Analyst may raise an incident's tier mid-response.</t>
@@ -1021,10 +1026,8 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="B42" s="26">
+        <v>46034</v>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
@@ -1039,11 +1042,11 @@
       <c r="E42" s="14" t="n"/>
     </row>
     <row r="43"/>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="2" t="n"/>
+    <row r="44">
+      <c r="A44"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A15:E15"/>
@@ -1071,12 +1074,11 @@
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A44:E44"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>